--- a/ig/DM-JANVIER-2026/CodeSystem-tre-r407-composition-foyer.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-tre-r407-composition-foyer.xlsx
@@ -244,7 +244,7 @@
     <t>Avec un(e) ou des colocataires</t>
   </si>
   <si>
-    <t xml:space="preserve">Avec d'autres types de personnes </t>
+    <t>Avec d'autres types de personnes</t>
   </si>
 </sst>
 </file>
